--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>124078137</v>
       </c>
       <c r="B5" t="n">
-        <v>58338</v>
+        <v>58339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Tommy Carlström, Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124078113</v>
       </c>
       <c r="B2" t="n">
-        <v>56788</v>
+        <v>56789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -801,7 +801,7 @@
         <v>124078118</v>
       </c>
       <c r="B3" t="n">
-        <v>57017</v>
+        <v>57018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -919,7 +919,7 @@
         <v>124078121</v>
       </c>
       <c r="B4" t="n">
-        <v>57246</v>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1037,7 +1037,7 @@
         <v>124078137</v>
       </c>
       <c r="B5" t="n">
-        <v>58339</v>
+        <v>58340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>124078125</v>
       </c>
       <c r="B6" t="n">
-        <v>57257</v>
+        <v>57258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
         <v>125870051</v>
       </c>
       <c r="B7" t="n">
-        <v>56806</v>
+        <v>56807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124078113</v>
       </c>
       <c r="B2" t="n">
-        <v>56789</v>
+        <v>56793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>124078118</v>
       </c>
       <c r="B3" t="n">
-        <v>57018</v>
+        <v>57022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>124078121</v>
       </c>
       <c r="B4" t="n">
-        <v>57247</v>
+        <v>57251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>124078137</v>
       </c>
       <c r="B5" t="n">
-        <v>58340</v>
+        <v>58344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>124078125</v>
       </c>
       <c r="B6" t="n">
-        <v>57258</v>
+        <v>57262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125870051</v>
       </c>
       <c r="B7" t="n">
-        <v>56807</v>
+        <v>56811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124078113</v>
       </c>
       <c r="B2" t="n">
-        <v>56793</v>
+        <v>56794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -801,7 +801,7 @@
         <v>124078118</v>
       </c>
       <c r="B3" t="n">
-        <v>57022</v>
+        <v>57023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -919,7 +919,7 @@
         <v>124078121</v>
       </c>
       <c r="B4" t="n">
-        <v>57251</v>
+        <v>57252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1037,7 +1037,7 @@
         <v>124078137</v>
       </c>
       <c r="B5" t="n">
-        <v>58344</v>
+        <v>58347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         <v>124078125</v>
       </c>
       <c r="B6" t="n">
-        <v>57262</v>
+        <v>57263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Wigren, Inge Schentz, Tommy Carlström, Lennart Nyman</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
         <v>125870051</v>
       </c>
       <c r="B7" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,6 +1392,363 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127404018</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57913</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102981</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127403911</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57069</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127404011</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57743</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1749,6 +1749,244 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127587818</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57655</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Johan Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Johan Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127587286</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57079</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Johan Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Johan Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>127404018</v>
       </c>
       <c r="B8" t="n">
-        <v>57913</v>
+        <v>57917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127403911</v>
       </c>
       <c r="B9" t="n">
-        <v>57069</v>
+        <v>57073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127404011</v>
       </c>
       <c r="B10" t="n">
-        <v>57743</v>
+        <v>57747</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1987,6 +1987,238 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127715090</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57645</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100004</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfiskare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alcedo atthis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Carlström, Gunnar E Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127715097</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58166</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Carlström, Gunnar E Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>127404018</v>
       </c>
       <c r="B8" t="n">
-        <v>57917</v>
+        <v>57919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127403911</v>
       </c>
       <c r="B9" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127404011</v>
       </c>
       <c r="B10" t="n">
-        <v>57747</v>
+        <v>57749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>127587818</v>
       </c>
       <c r="B11" t="n">
-        <v>57655</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127587286</v>
       </c>
       <c r="B12" t="n">
-        <v>57079</v>
+        <v>57081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>127715090</v>
       </c>
       <c r="B13" t="n">
-        <v>57645</v>
+        <v>57647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127715097</v>
       </c>
       <c r="B14" t="n">
-        <v>58166</v>
+        <v>58168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,6 +2219,129 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127778529</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57600</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lennart Kärnhall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lennart Kärnhall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>127404018</v>
       </c>
       <c r="B8" t="n">
-        <v>57919</v>
+        <v>57922</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127403911</v>
       </c>
       <c r="B9" t="n">
-        <v>57075</v>
+        <v>57078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127404011</v>
       </c>
       <c r="B10" t="n">
-        <v>57749</v>
+        <v>57752</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>127587818</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127587286</v>
       </c>
       <c r="B12" t="n">
-        <v>57081</v>
+        <v>57084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>127715090</v>
       </c>
       <c r="B13" t="n">
-        <v>57647</v>
+        <v>57650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127715097</v>
       </c>
       <c r="B14" t="n">
-        <v>58168</v>
+        <v>58171</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>127778529</v>
       </c>
       <c r="B15" t="n">
-        <v>57600</v>
+        <v>57603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,7 +1397,7 @@
         <v>127404018</v>
       </c>
       <c r="B8" t="n">
-        <v>57922</v>
+        <v>57928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127403911</v>
       </c>
       <c r="B9" t="n">
-        <v>57078</v>
+        <v>57084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127404011</v>
       </c>
       <c r="B10" t="n">
-        <v>57752</v>
+        <v>57758</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>127587818</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127587286</v>
       </c>
       <c r="B12" t="n">
-        <v>57084</v>
+        <v>57090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>127715090</v>
       </c>
       <c r="B13" t="n">
-        <v>57650</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127715097</v>
       </c>
       <c r="B14" t="n">
-        <v>58171</v>
+        <v>58177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>127778529</v>
       </c>
       <c r="B15" t="n">
-        <v>57603</v>
+        <v>57609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,6 +2341,122 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128094802</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102931</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bläsand</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Mareca penelope</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Carlström, Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1992,7 +1992,7 @@
         <v>127715090</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127715097</v>
       </c>
       <c r="B14" t="n">
-        <v>58177</v>
+        <v>58178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>127778529</v>
       </c>
       <c r="B15" t="n">
-        <v>57609</v>
+        <v>57610</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1992,7 +1992,7 @@
         <v>127715090</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127715097</v>
       </c>
       <c r="B14" t="n">
-        <v>58178</v>
+        <v>58189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>127778529</v>
       </c>
       <c r="B15" t="n">
-        <v>57610</v>
+        <v>57622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>128094802</v>
       </c>
       <c r="B16" t="n">
-        <v>56816</v>
+        <v>56828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -2347,7 +2347,7 @@
         <v>128094802</v>
       </c>
       <c r="B16" t="n">
-        <v>56828</v>
+        <v>56832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2458,6 +2458,122 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132462105</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57335</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100091</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Storspov</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Numenius arquata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Klas Kärvegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Klas Kärvegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2574,6 +2574,122 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132640370</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57253</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Carlström, Gunnar E Gustafsson, Inge Schentz, Johan Löwhagen, Kenneth Petersson, Klas Kärvegård, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Thomas  Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2463,7 +2463,7 @@
         <v>132462105</v>
       </c>
       <c r="B17" t="n">
-        <v>57335</v>
+        <v>57336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>132640370</v>
       </c>
       <c r="B18" t="n">
-        <v>57253</v>
+        <v>57254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,6 +2689,127 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132663077</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57080</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100007</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Årta</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Spatula querquedula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gunnar E Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gunnar E Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -2463,7 +2463,7 @@
         <v>132462105</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>57340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>132640370</v>
       </c>
       <c r="B18" t="n">
-        <v>57254</v>
+        <v>57258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>132663077</v>
       </c>
       <c r="B19" t="n">
-        <v>57080</v>
+        <v>57084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Gunnar E Gustafsson, Inge Schentz, Johan Löwhagen, Kenneth Petersson, Klas Kärvegård, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Thomas  Gustafsson</t>
+          <t>Thomas  Gustafsson , Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Kärvegård, Kenneth Petersson, Johan Löwhagen, Inge Schentz, Gunnar E Gustafsson, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2811,6 +2811,240 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132836725</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57397</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100103</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brushane</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calidris pugnax</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Andresén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Andresén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132836706</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57247</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S21" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Andresén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Andresén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -2463,7 +2463,7 @@
         <v>132462105</v>
       </c>
       <c r="B17" t="n">
-        <v>57340</v>
+        <v>57341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>132640370</v>
       </c>
       <c r="B18" t="n">
-        <v>57258</v>
+        <v>57259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Thomas  Gustafsson , Sussie Nielsen, Michael Engström, Lennart Kärnhall, Klas Kärvegård, Kenneth Petersson, Johan Löwhagen, Inge Schentz, Gunnar E Gustafsson, Tommy Carlström</t>
+          <t>Tommy Carlström, Gunnar E Gustafsson, Inge Schentz, Johan Löwhagen, Kenneth Petersson, Klas Kärvegård, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Thomas  Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
         <v>132836725</v>
       </c>
       <c r="B20" t="n">
-        <v>57397</v>
+        <v>57398</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>132836706</v>
       </c>
       <c r="B21" t="n">
-        <v>57247</v>
+        <v>57248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3045,6 +3045,121 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133062116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58083</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103035</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corvus corone</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mathias Bergström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mathias Bergström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3947,6 +3947,229 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133526520</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58358</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S30" t="n">
+        <v>100</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristina Sandwall</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristina Sandwall</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133525357</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S31" t="n">
+        <v>100</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristina Sandwall</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristina Sandwall</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4170,6 +4170,125 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133557342</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57779</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S32" t="n">
+        <v>100</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Inge Schentz</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Inge Schentz, Michael Engström</t>
+          <t>Michael Engström, Inge Schentz</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michael Engström, Inge Schentz</t>
+          <t>Inge Schentz, Michael Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -3165,7 +3165,7 @@
         <v>133168383</v>
       </c>
       <c r="B23" t="n">
-        <v>57947</v>
+        <v>57954</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>133177975</v>
       </c>
       <c r="B24" t="n">
-        <v>57551</v>
+        <v>57558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>133178002</v>
       </c>
       <c r="B25" t="n">
-        <v>57895</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>133177980</v>
       </c>
       <c r="B26" t="n">
-        <v>57322</v>
+        <v>57329</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>133177969</v>
       </c>
       <c r="B27" t="n">
-        <v>58217</v>
+        <v>58224</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>133168388</v>
       </c>
       <c r="B28" t="n">
-        <v>58681</v>
+        <v>58688</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>133427461</v>
       </c>
       <c r="B29" t="n">
-        <v>58208</v>
+        <v>58215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>133526520</v>
       </c>
       <c r="B30" t="n">
-        <v>58358</v>
+        <v>58365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>133525357</v>
       </c>
       <c r="B31" t="n">
-        <v>58393</v>
+        <v>58400</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>133557342</v>
       </c>
       <c r="B32" t="n">
-        <v>57779</v>
+        <v>57786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -3833,7 +3833,7 @@
         <v>133427461</v>
       </c>
       <c r="B29" t="n">
-        <v>58215</v>
+        <v>58225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>133526520</v>
       </c>
       <c r="B30" t="n">
-        <v>58365</v>
+        <v>58375</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>133525357</v>
       </c>
       <c r="B31" t="n">
-        <v>58400</v>
+        <v>58410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>133557342</v>
       </c>
       <c r="B32" t="n">
-        <v>57786</v>
+        <v>57796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127715090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132663077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132836706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640370</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778529</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133178002</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,6 +1523,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132462105</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132836725</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1726,6 +1771,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133427461</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1850,6 +1900,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132319020</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1969,6 +2024,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133425882</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2085,6 +2145,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133168383</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2208,6 +2273,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127404011</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2324,6 +2394,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128094802</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2448,6 +2523,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870051</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2566,6 +2646,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078118</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2675,6 +2760,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133177980</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2794,6 +2884,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127403911</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2913,6 +3008,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127587286</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3031,6 +3131,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078121</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3140,6 +3245,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133177975</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3259,6 +3369,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132241752</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3378,6 +3493,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133557342</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3497,6 +3617,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127587818</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3620,6 +3745,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870183</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3729,6 +3859,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133177968</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3844,6 +3979,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127404018</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3953,6 +4093,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133177969</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4071,6 +4216,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078135</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4180,6 +4330,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133177967</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4296,6 +4451,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127715097</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4403,6 +4563,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133525357</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4518,6 +4683,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133062116</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4634,6 +4804,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133526520</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4750,6 +4925,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133168388</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4868,8 +5048,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778529</v>
+        <v>135749428</v>
       </c>
       <c r="B6" t="n">
-        <v>57890</v>
+        <v>57926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,16 +1179,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100082</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,21 +1198,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
@@ -1249,22 +1242,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,27 +1272,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lennart Kärnhall</t>
+          <t>Klas Kärvegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lennart Kärnhall</t>
+          <t>Klas Kärvegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127778529</t>
+          <t>https://artportalen.se/Sighting/135749428</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133178002</v>
+        <v>127778529</v>
       </c>
       <c r="B7" t="n">
-        <v>57912</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,11 +1319,15 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1343,13 +1340,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521919</v>
+        <v>521950</v>
       </c>
       <c r="R7" t="n">
-        <v>6358435</v>
+        <v>6358422</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,12 +1370,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,44 +1400,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Lennart Kärnhall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Lennart Kärnhall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133178002</t>
+          <t>https://artportalen.se/Sighting/127778529</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132462105</v>
+        <v>133178002</v>
       </c>
       <c r="B8" t="n">
-        <v>57362</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100091</v>
+        <v>100082</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1440,27 +1447,30 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521950</v>
+        <v>521919</v>
       </c>
       <c r="R8" t="n">
-        <v>6358422</v>
+        <v>6358435</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,22 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,44 +1514,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Klas Kärvegård</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Kärvegård</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132462105</t>
+          <t>https://artportalen.se/Sighting/133178002</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132836725</v>
+        <v>132462105</v>
       </c>
       <c r="B9" t="n">
-        <v>57436</v>
+        <v>57362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100103</v>
+        <v>100091</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brushane</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calidris pugnax</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1561,17 +1561,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
@@ -1608,22 +1605,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,44 +1635,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Andresén</t>
+          <t>Klas Kärvegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Andresén</t>
+          <t>Klas Kärvegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132836725</t>
+          <t>https://artportalen.se/Sighting/132462105</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133427461</v>
+        <v>135764729</v>
       </c>
       <c r="B10" t="n">
-        <v>58225</v>
+        <v>57865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100124</v>
+        <v>100100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1685,16 +1682,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1732,22 +1725,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,44 +1755,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Tomas Claesson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Inge Schentz, Michael Engström</t>
+          <t>Tomas Claesson, Inge Schentz</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133427461</t>
+          <t>https://artportalen.se/Sighting/135764729</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132319020</v>
+        <v>132836725</v>
       </c>
       <c r="B11" t="n">
-        <v>57087</v>
+        <v>57436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102106</v>
+        <v>100103</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skedand</t>
+          <t>Brushane</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spatula clypeata</t>
+          <t>Calidris pugnax</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1809,16 +1802,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1856,27 +1849,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 hanar 1 hona</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1891,61 +1879,61 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Johan Andresén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Inge Schentz, Michael Engström</t>
+          <t>Johan Andresén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132319020</t>
+          <t>https://artportalen.se/Sighting/132836725</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133425882</v>
+        <v>133427461</v>
       </c>
       <c r="B12" t="n">
-        <v>57442</v>
+        <v>58225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102112</v>
+        <v>100124</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mosnäppa</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calidris temminckii</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Leisler, 1812)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1990,7 +1978,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2000,7 +1988,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,61 +2003,64 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Andresén</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Andresén</t>
+          <t>Inge Schentz, Michael Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133425882</t>
+          <t>https://artportalen.se/Sighting/133427461</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133168383</v>
+        <v>132319020</v>
       </c>
       <c r="B13" t="n">
-        <v>57964</v>
+        <v>57087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102119</v>
+        <v>102106</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Skedand</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Spatula clypeata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
@@ -2106,22 +2097,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 hanar 1 hona</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,65 +2132,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gunnar E Gustafsson</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gunnar E Gustafsson</t>
+          <t>Inge Schentz, Michael Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133168383</t>
+          <t>https://artportalen.se/Sighting/132319020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127404011</v>
+        <v>133425882</v>
       </c>
       <c r="B14" t="n">
-        <v>58039</v>
+        <v>57442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102626</v>
+        <v>102112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Mosnäppa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Calidris temminckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Leisler, 1812)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2234,22 +2226,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,27 +2256,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Johan Andresén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Johan Andresén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127404011</t>
+          <t>https://artportalen.se/Sighting/133425882</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128094802</v>
+        <v>133168383</v>
       </c>
       <c r="B15" t="n">
-        <v>57094</v>
+        <v>57964</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,21 +2284,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102931</v>
+        <v>102119</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2316,7 +2308,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2355,22 +2347,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2385,44 +2377,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Carlström</t>
+          <t>Gunnar E Gustafsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström</t>
+          <t>Gunnar E Gustafsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128094802</t>
+          <t>https://artportalen.se/Sighting/133168383</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125870051</v>
+        <v>127404011</v>
       </c>
       <c r="B16" t="n">
-        <v>57105</v>
+        <v>58039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102932</v>
+        <v>102626</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2432,14 +2424,18 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2479,27 +2475,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1p+2 hanar+1 hane</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2514,44 +2505,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Söderberg</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Söderberg</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125870051</t>
+          <t>https://artportalen.se/Sighting/127404011</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124078118</v>
+        <v>128094802</v>
       </c>
       <c r="B17" t="n">
-        <v>57317</v>
+        <v>57094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102952</v>
+        <v>102931</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2561,16 +2552,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
@@ -2607,22 +2596,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,49 +2631,49 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Tommy Carlström, Ingela Carlström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124078118</t>
+          <t>https://artportalen.se/Sighting/128094802</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133177980</v>
+        <v>125870051</v>
       </c>
       <c r="B18" t="n">
-        <v>57339</v>
+        <v>57105</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102952</v>
+        <v>102932</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2701,13 +2690,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521919</v>
+        <v>521950</v>
       </c>
       <c r="R18" t="n">
-        <v>6358435</v>
+        <v>6358422</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,12 +2720,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1p+2 hanar+1 hane</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2751,44 +2755,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Håkan Söderberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Håkan Söderberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133177980</t>
+          <t>https://artportalen.se/Sighting/125870051</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127403911</v>
+        <v>124078118</v>
       </c>
       <c r="B19" t="n">
-        <v>57364</v>
+        <v>57317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102954</v>
+        <v>102952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2798,11 +2802,10 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2845,22 +2848,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2875,61 +2878,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127403911</t>
+          <t>https://artportalen.se/Sighting/124078118</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127587286</v>
+        <v>133177980</v>
       </c>
       <c r="B20" t="n">
-        <v>57369</v>
+        <v>57339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102961</v>
+        <v>102952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2939,13 +2942,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521950</v>
+        <v>521919</v>
       </c>
       <c r="R20" t="n">
-        <v>6358422</v>
+        <v>6358435</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2969,22 +2972,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2999,27 +2992,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Johan Johansson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Johan Johansson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127587286</t>
+          <t>https://artportalen.se/Sighting/133177980</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124078121</v>
+        <v>127403911</v>
       </c>
       <c r="B21" t="n">
-        <v>57546</v>
+        <v>57364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,16 +3020,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3046,13 +3039,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3092,22 +3086,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3122,27 +3116,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tommy Carlström</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124078121</t>
+          <t>https://artportalen.se/Sighting/127403911</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133177975</v>
+        <v>135739604</v>
       </c>
       <c r="B22" t="n">
-        <v>57568</v>
+        <v>57413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,33 +3144,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102963</v>
+        <v>102957</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Svartsnäppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Tringa erythropus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3186,13 +3180,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521919</v>
+        <v>521950</v>
       </c>
       <c r="R22" t="n">
-        <v>6358435</v>
+        <v>6358422</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3216,12 +3210,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3236,44 +3240,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Jonny Fleur</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Jonny Fleur</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133177975</t>
+          <t>https://artportalen.se/Sighting/135739604</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132241752</v>
+        <v>127587286</v>
       </c>
       <c r="B23" t="n">
-        <v>57557</v>
+        <v>57369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102964</v>
+        <v>102961</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3283,7 +3287,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3330,22 +3334,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3360,44 +3364,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lennart Kärnhall</t>
+          <t>Lars Johan Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lennart Kärnhall</t>
+          <t>Lars Johan Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132241752</t>
+          <t>https://artportalen.se/Sighting/127587286</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133557342</v>
+        <v>124078121</v>
       </c>
       <c r="B24" t="n">
-        <v>57796</v>
+        <v>57546</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102976</v>
+        <v>102963</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3407,14 +3411,13 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3454,22 +3457,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3484,61 +3487,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133557342</t>
+          <t>https://artportalen.se/Sighting/124078121</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127587818</v>
+        <v>133177975</v>
       </c>
       <c r="B25" t="n">
-        <v>57947</v>
+        <v>57568</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102977</v>
+        <v>102963</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3548,13 +3551,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521950</v>
+        <v>521919</v>
       </c>
       <c r="R25" t="n">
-        <v>6358422</v>
+        <v>6358435</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3578,22 +3581,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3608,44 +3601,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Johan Johansson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Johan Johansson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127587818</t>
+          <t>https://artportalen.se/Sighting/133177975</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125870183</v>
+        <v>132241752</v>
       </c>
       <c r="B26" t="n">
-        <v>58209</v>
+        <v>57557</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102980</v>
+        <v>102964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3655,14 +3648,10 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
@@ -3706,22 +3695,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3736,54 +3725,54 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Söderberg</t>
+          <t>Lennart Kärnhall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Söderberg</t>
+          <t>Lennart Kärnhall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125870183</t>
+          <t>https://artportalen.se/Sighting/132241752</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133177968</v>
+        <v>133557342</v>
       </c>
       <c r="B27" t="n">
-        <v>58231</v>
+        <v>57796</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102980</v>
+        <v>102976</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3800,13 +3789,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521919</v>
+        <v>521950</v>
       </c>
       <c r="R27" t="n">
-        <v>6358435</v>
+        <v>6358422</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3830,12 +3819,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3850,57 +3849,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133177968</t>
+          <t>https://artportalen.se/Sighting/133557342</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127404018</v>
+        <v>127587818</v>
       </c>
       <c r="B28" t="n">
-        <v>58212</v>
+        <v>57947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102981</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3940,22 +3943,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3970,57 +3973,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Lars Johan Johansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Inge Schentz</t>
+          <t>Lars Johan Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127404018</t>
+          <t>https://artportalen.se/Sighting/127587818</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133177969</v>
+        <v>125870183</v>
       </c>
       <c r="B29" t="n">
-        <v>58234</v>
+        <v>58209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
@@ -4034,13 +4041,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521919</v>
+        <v>521950</v>
       </c>
       <c r="R29" t="n">
-        <v>6358435</v>
+        <v>6358422</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4064,12 +4071,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4084,27 +4101,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Håkan Söderberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Håkan Söderberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133177969</t>
+          <t>https://artportalen.se/Sighting/125870183</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124078135</v>
+        <v>133177968</v>
       </c>
       <c r="B30" t="n">
-        <v>58541</v>
+        <v>58231</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4112,16 +4129,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4131,10 +4148,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4147,13 +4165,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521950</v>
+        <v>521919</v>
       </c>
       <c r="R30" t="n">
-        <v>6358422</v>
+        <v>6358435</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4177,22 +4195,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>18:47</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4207,61 +4215,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tommy Carlström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124078135</t>
+          <t>https://artportalen.se/Sighting/133177968</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133177967</v>
+        <v>127404018</v>
       </c>
       <c r="B31" t="n">
-        <v>58563</v>
+        <v>58212</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102987</v>
+        <v>102981</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4271,13 +4275,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521919</v>
+        <v>521950</v>
       </c>
       <c r="R31" t="n">
-        <v>6358435</v>
+        <v>6358422</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4301,12 +4305,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4321,44 +4335,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Inge Schentz</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133177967</t>
+          <t>https://artportalen.se/Sighting/127404018</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127715097</v>
+        <v>133177969</v>
       </c>
       <c r="B32" t="n">
-        <v>58463</v>
+        <v>58234</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102995</v>
+        <v>102981</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4368,27 +4382,30 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521950</v>
+        <v>521919</v>
       </c>
       <c r="R32" t="n">
-        <v>6358422</v>
+        <v>6358435</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4412,22 +4429,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4442,27 +4449,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tommy Carlström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Gunnar E Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127715097</t>
+          <t>https://artportalen.se/Sighting/133177969</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133525357</v>
+        <v>124078135</v>
       </c>
       <c r="B33" t="n">
-        <v>58410</v>
+        <v>58541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4470,24 +4477,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103001</v>
+        <v>102987</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
@@ -4524,22 +4542,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4554,44 +4572,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristina Sandwall</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristina Sandwall</t>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133525357</t>
+          <t>https://artportalen.se/Sighting/124078135</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133062116</v>
+        <v>133177967</v>
       </c>
       <c r="B34" t="n">
-        <v>58104</v>
+        <v>58563</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103035</v>
+        <v>102987</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4599,7 +4617,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
@@ -4614,13 +4636,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521950</v>
+        <v>521919</v>
       </c>
       <c r="R34" t="n">
-        <v>6358422</v>
+        <v>6358435</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4644,22 +4666,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4674,54 +4686,54 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mathias Bergström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mathias Bergström</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133062116</t>
+          <t>https://artportalen.se/Sighting/133177967</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133526520</v>
+        <v>127715097</v>
       </c>
       <c r="B35" t="n">
-        <v>58375</v>
+        <v>58463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103037</v>
+        <v>102995</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4765,22 +4777,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4795,27 +4807,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristina Sandwall</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristina Sandwall</t>
+          <t>Tommy Carlström, Gunnar E Gustafsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133526520</t>
+          <t>https://artportalen.se/Sighting/127715097</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133168388</v>
+        <v>133525357</v>
       </c>
       <c r="B36" t="n">
-        <v>58698</v>
+        <v>58410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4823,33 +4835,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Prästgårdens våtmark, Skirö, Sm</t>
@@ -4886,22 +4889,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4916,27 +4919,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gunnar E Gustafsson</t>
+          <t>Kristina Sandwall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gunnar E Gustafsson</t>
+          <t>Kristina Sandwall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133168388</t>
+          <t>https://artportalen.se/Sighting/133525357</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124078137</v>
+        <v>133062116</v>
       </c>
       <c r="B37" t="n">
-        <v>58649</v>
+        <v>58104</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4944,29 +4947,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103057</v>
+        <v>103035</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -5009,22 +5009,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5039,16 +5039,381 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tommy Carlström</t>
+          <t>Mathias Bergström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+          <t>Mathias Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133062116</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133526520</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58375</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S38" t="n">
+        <v>100</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristina Sandwall</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristina Sandwall</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133526520</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133168388</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S39" t="n">
+        <v>100</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Gunnar E Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gunnar E Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133168388</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124078137</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Prästgårdens våtmark, Skirö, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>521950</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6358422</v>
+      </c>
+      <c r="S40" t="n">
+        <v>100</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skirö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tommy Carlström, Inge Schentz, Klas Wigren, Lennart Kärnhall, Michael Engström, Sussie Nielsen, Lennart Nyman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124078137</t>
         </is>
@@ -5092,6 +5457,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>135749428</v>
       </c>
       <c r="B6" t="n">
-        <v>57926</v>
+        <v>57928</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>135764729</v>
       </c>
       <c r="B10" t="n">
-        <v>57865</v>
+        <v>57867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>135739604</v>
       </c>
       <c r="B22" t="n">
-        <v>57413</v>
+        <v>57415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>135749428</v>
       </c>
       <c r="B6" t="n">
-        <v>57928</v>
+        <v>57929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>135764729</v>
       </c>
       <c r="B10" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>135739604</v>
       </c>
       <c r="B22" t="n">
-        <v>57415</v>
+        <v>57416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>135749428</v>
       </c>
       <c r="B6" t="n">
-        <v>57929</v>
+        <v>57933</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>135764729</v>
       </c>
       <c r="B10" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>135739604</v>
       </c>
       <c r="B22" t="n">
-        <v>57416</v>
+        <v>57420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>135749428</v>
       </c>
       <c r="B6" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>135764729</v>
       </c>
       <c r="B10" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>135739604</v>
       </c>
       <c r="B22" t="n">
-        <v>57420</v>
+        <v>57421</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29114-2023 artfynd.xlsx
+++ b/artfynd/A 29114-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>135749428</v>
       </c>
       <c r="B6" t="n">
-        <v>57934</v>
+        <v>57939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>135764729</v>
       </c>
       <c r="B10" t="n">
-        <v>57873</v>
+        <v>57878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>135739604</v>
       </c>
       <c r="B22" t="n">
-        <v>57421</v>
+        <v>57426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
